--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_056_Belgium.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_056_Belgium.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R281bc48656364626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1ddeaa1780a244bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb2a6e7d0de2c4ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbb9affd6d66444ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5aaca9084c2c4257"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra3acf22a8795402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6e9a72e6f53a4c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb74798cd753c4ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R120c8c0e2ce34db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5ce9c4b1c8b343f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc505d65f03774dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6ef593cd87e84ed4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ056CommercialTable" displayName="EEZ056CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ056CommercialTable" displayName="EEZ056CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ056FunctionalTable" displayName="EEZ056FunctionalTable" ref="A1:O24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O24"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ056FunctionalTable" displayName="EEZ056FunctionalTable" ref="A1:E24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ056ValidationTable" displayName="EEZ056ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ056ValidationTable" displayName="EEZ056ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10945,7 +10899,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra929ac1301084349"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc01e5b1d77414c2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10955,20 +10909,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10976,660 +10920,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.0028653886999999998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1099999999999994</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931323</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.0028653886999999998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$154,A2,'Species'!$U$2:$U$154))</x:f>
-        <x:v>0.3691335708201571</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1099999999999994</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931323</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>0.3691335708201567</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3.885780586188048e-16</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>1.0526760211905017e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>484.4840169687</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.276903698238854</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1891.9240512144104</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>484.4840169687</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2000.5417189715934</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$154,A3,'Species'!$U$2:$U$154))</x:f>
-        <x:v>969230.4881208257</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.276903698238854</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1891.9240512144104</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>916606.9641320541</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>52623.5239887716</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0574112199099441</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0574112199099441</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1407.2283228161998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1545620920530646</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>142.7453901852074</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1407.2283228161998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>144.4669398550154</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$154,A4,'Species'!$U$2:$U$154))</x:f>
-        <x:v>203297.96947456212</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1545620920530646</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>142.7453901852074</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>200875.35602007346</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2422.613454488659</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.012060282069875</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.012060282069875049</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1745.0309281759</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.302035674545842</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>200.4636688831701</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1745.0309281759</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>261.9181541531588</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$154,A5,'Species'!$U$2:$U$154))</x:f>
-        <x:v>457055.2796480052</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.302035674545842</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>200.4636688831701</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>349815.3021767446</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>107239.97747126059</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3065617107197829</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3065617107197828</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>54.692053183999995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3297437086904043</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>213.67007806911158</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>54.692053183999995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>219.41524031695076</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$154,A6,'Species'!$U$2:$U$154))</x:f>
-        <x:v>12000.26999279481</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3297437086904043</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>213.67007806911158</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>11686.055273585282</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>314.214719209529</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0268880055633287</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.026888005563328807</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>255.0159570159</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.229200298738944</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>16.9511941755591</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>255.0159570159</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>79.89073214707221</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$154,A7,'Species'!$U$2:$U$154))</x:f>
-        <x:v>20373.411515186548</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.229200298738944</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>16.9511941755591</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4322.825005242554</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>16050.586509943994</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>4.712985487610178</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>3.712985487610178</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>197.01412378570004</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6897705837824324</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>489.5201618534684</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>197.01412378570004</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>982.963470550185</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$154,A8,'Species'!$U$2:$U$154))</x:f>
-        <x:v>193657.68686379545</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6897705837824324</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>489.5201618534684</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>96442.38576299514</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>97215.30110080031</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.0080142701955195</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.0080142701955195</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>112.719001407</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6398002235507683</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>436.315080141479</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>112.719001407</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>539.8929899717633</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$154,A9,'Species'!$U$2:$U$154))</x:f>
-        <x:v>60856.19869625662</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6398002235507683</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>436.315080141479</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>49181.000132362686</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>11675.198563893937</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2373924591299899</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2373924591299899</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.293067018</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4634531077393356</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>290.70540579281516</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.293067018</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>293.4370656709694</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$154,A10,'Species'!$U$2:$U$154))</x:f>
-        <x:v>85.99672580686118</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4634531077393356</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>290.70540579281516</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>85.19616639218027</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0.8005594146809045</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0093966600679627</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00939666006796268</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>109.4550018143</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8937614704679055</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>782.9994742854618</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>109.4550018143</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>800.5568848203885</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$154,A11,'Species'!$U$2:$U$154))</x:f>
-        <x:v>87624.95528046599</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8937614704679055</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>782.9994742854618</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>85703.20887851117</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1921.7464019548206</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0224232724433806</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.02242327244338071</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>116.8869654519</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9203122040458225</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>832.361921405326</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>116.8869654519</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>891.6753404048347</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$154,A12,'Species'!$U$2:$U$154))</x:f>
-        <x:v>104225.22470821108</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9203122040458225</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>832.361921405326</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>97292.25915078145</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>6932.965557429634</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0712591692077482</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0712591692077483</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R584fd8d375df4826"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82b03018452d47c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11639,20 +11154,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11660,1308 +11165,459 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>61.7139144487</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.055072874565252</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1135.2012863396503</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>61.7139144487</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1237.5831058226809</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$154,A2,'Species'!$U$2:$U$154))</x:f>
-        <x:v>76376.09791589736</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.055072874565252</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1135.2012863396503</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>70057.71506721938</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>6318.382848677982</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.090188251823737</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.09018825182373681</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3.7911990302</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.363078547028269</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2307.1644275525505</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3.7911990302</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2314.5324787310087</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$154,A3,'Species'!$U$2:$U$154))</x:f>
-        <x:v>8774.853288731403</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.363078547028269</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2307.1644275525505</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8746.919540249168</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>27.933748482235387</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0031935526963176</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0031935526963175493</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>85.4575409016</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.09374269620768</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1240.916891328203</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>85.4575409016</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1244.5893427951073</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$154,A4,'Species'!$U$2:$U$154))</x:f>
-        <x:v>106359.54466760834</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.09374269620768</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1240.916891328203</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>106045.70599616623</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>313.8386714421067</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0029594660952463</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0029594660952462575</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>29.886499595</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8045528166514946</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>637.60661874329</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>29.886499595</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>675.1084445503008</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$154,A5,'Species'!$U$2:$U$154))</x:f>
-        <x:v>20176.628254633644</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8045528166514946</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>637.60661874329</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>19055.829952840657</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1120.7983017929873</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.058816556642599</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05881655664259901</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>802.477826399</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.311002690689773</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>204.64573155979784</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>802.477826399</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>279.75140431678227</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$154,A6,'Species'!$U$2:$U$154))</x:f>
-        <x:v>224494.29886819926</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.311002690689773</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>204.64573155979784</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>164223.6618439398</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>60270.63702425946</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3670033681354279</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3670033681354279</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.1266030537</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.039714150686399</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1095.7567400169369</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.1266030537</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1096.113573723866</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$154,A7,'Species'!$U$2:$U$154))</x:f>
-        <x:v>138.77132563546152</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.039714150686399</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1095.7567400169369</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>138.7261493985012</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.04517623696031592</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0003256504787035</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00032565047870350536</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>32.483008064</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.816830355261552</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>655.889011942774</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>32.483008064</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>689.4634686820533</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$154,A8,'Species'!$U$2:$U$154))</x:f>
-        <x:v>22395.847413032552</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.816830355261552</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>655.889011942774</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>21305.248064026124</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1090.5993490064284</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0511892349588694</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0511892349588693</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3.8172645458</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2882183771267615</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>194.1862062366628</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3.8172645458</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>195.65320767199236</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$154,A9,'Species'!$U$2:$U$154))</x:f>
-        <x:v>746.860052918341</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2882183771267615</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>194.1862062366628</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>741.2601203506198</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5.5999325677212255</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0075546119560195</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.007554611956019473</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>45.911193261</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.065906821250437</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1163.87629063488</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>45.911193261</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1209.250916366782</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$154,A10,'Species'!$U$2:$U$154))</x:f>
-        <x:v>55518.15252235667</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.065906821250437</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1163.87629063488</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>53434.94931123378</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2083.203211122891</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0389857806168992</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03898578061689923</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>509.5456188952999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.0976762119568644</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>125.22072443271956</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>509.5456188952999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>127.30537119630645</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$154,A11,'Species'!$U$2:$U$154))</x:f>
-        <x:v>64867.89415491786</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.0976762119568644</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>125.22072443271956</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>63805.6715295879</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1062.2226253299668</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.016647777538669</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01664777753866902</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>32.3238633549</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.459999999999999</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2884.0315031266</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>32.3238633549</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2884.031503126606</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$154,A12,'Species'!$U$2:$U$154))</x:f>
-        <x:v>93223.04021829125</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.459999999999999</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2884.0315031266</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>93223.04021829106</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1.8917489796876907e-10</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.000000000000002</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>2.0292719216815623e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>385.92061585230005</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.325962460199954</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2118.17803502519</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>385.92061585230005</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2197.743087762676</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$154,A13,'Species'!$U$2:$U$154))</x:f>
-        <x:v>848154.3659145075</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.325962460199954</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2118.17803502519</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>817448.5717617362</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>30705.794152771356</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.037562967522954</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.037562967522954155</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>249.2758960123</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.611673343809979</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>408.9529485588543</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>249.2758960123</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>511.45851181710384</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$154,A14,'Species'!$U$2:$U$154))</x:f>
-        <x:v>127494.27880632608</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.611673343809979</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>408.9529485588543</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>101942.11267888044</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>25552.166127445642</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2506536842917455</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2506536842917455</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>82.06064285469998</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.555080946670614</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>358.9888391178772</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>82.06064285469998</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>484.5944468958951</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$154,A15,'Species'!$U$2:$U$154))</x:f>
-        <x:v>39766.13183609492</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.555080946670614</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>358.9888391178772</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>29458.85491567547</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>10307.276920419452</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3498872223622924</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.3498872223622923</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>0.8856285745999999</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3404828121418664</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>219.01951460820183</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>0.8856285745999999</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>230.39514424670867</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$154,A16,'Species'!$U$2:$U$154))</x:f>
-        <x:v>204.04452319397396</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3404828121418664</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>219.01951460820183</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>193.96994053204563</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>10.074582661928332</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0519388861711998</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.051938886171199905</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>268.3101772053</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.249675295502841</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>17.76950359027712</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>268.3101772053</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>78.61543456237824</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$154,A17,'Species'!$U$2:$U$154))</x:f>
-        <x:v>21093.321178503375</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.249675295502841</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>17.76950359027712</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4767.73865715747</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>16325.582521345905</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>4.4241773082166445</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>3.4241773082166445</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>897.6827039209</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.1868518430457216</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>153.7629997579567</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>897.6827039209</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>154.2082460929782</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$154,A18,'Species'!$U$2:$U$154))</x:f>
-        <x:v>138430.07531964424</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.1868518430457216</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>153.7629997579567</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>138030.38538571127</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>399.6899339329684</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0028956662898252</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0028956662898250796</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>0.000247091</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.08</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>120.22644346174131</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>0.000247091</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>120.22644346174131</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$154,A19,'Species'!$U$2:$U$154))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>0.029706872141405122</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.08</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>120.22644346174131</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>0.029706872141405122</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>10.1059887711</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1127944170619664</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>129.65653676814873</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>10.1059887711</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>130.75494024317302</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$154,A20,'Species'!$U$2:$U$154))</x:f>
-        <x:v>1321.4079578633582</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1127944170619664</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>129.65653676814873</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1310.3075046786253</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>11.100453184732942</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0084716397831024</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.008471639783102298</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.0000052911</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.0000052911</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$154,A21,'Species'!$U$2:$U$154))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>0.000681625720296354</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>0.000681625720296354</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>942.5531017769</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.2944012700641188</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>196.97053751583837</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>942.5531017769</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>246.73514981955117</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$154,A22,'Species'!$U$2:$U$154))</x:f>
-        <x:v>232560.9807798061</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.2944012700641188</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>196.97053751583837</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>185655.19109421672</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>46905.78968558938</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.2526500304631154</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.25265003046311546</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>9.149719329000002</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.848392948669868</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>705.3309622087385</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>9.149719329000002</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>708.2930934705767</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$154,A23,'Species'!$U$2:$U$154))</x:f>
-        <x:v>6480.68300792494</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.848392948669868</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>705.3309622087385</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>6453.580338263464</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>27.102669661476284</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0041996331092036</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.004199633109203549</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>29.3430447979</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.8294906857944047</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>675.2905710510723</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>29.3430447979</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>675.8174518520374</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$154,A24,'Species'!$U$2:$U$154))</x:f>
-        <x:v>19830.54176489696</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.8294906857944047</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>675.2905710510723</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>19815.081477951087</x:v>
       </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>15.460286945872213</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0007802282803164</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.0007802282803164548</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G24">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O24">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbab8a038708346ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a38bbc9eeea4bad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13136,7 +11792,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13235,7 +11891,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2108407.8501594816</x:v>
+        <x:v>1812010.9218323133</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13249,7 +11905,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2108407.8501594816</x:v>
+        <x:v>1905854.5519366036</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13263,7 +11919,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-296396.92832716834</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13277,7 +11933,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-202553.29822287802</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13288,9 +11944,9 @@
         <x:v>EEZ_056</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13302,47 +11958,19 @@
         <x:v>EEZ_056</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_056</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_056</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a3d561275fe40e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b9843264ff24da1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13389,7 +12017,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
